--- a/RetinaLogik Data Classification.xlsx
+++ b/RetinaLogik Data Classification.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/reann/Library/CloudStorage/OneDrive-DalhousieUniversity/RIM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dalu-my.sharepoint.com/personal/rn623734_dal_ca/Documents/RIM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{600E7940-148B-6E48-B245-C7BAF064C3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EF71CE9-587E-40D2-8649-1AD4AD6DC67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14600" yWindow="0" windowWidth="14200" windowHeight="18000" xr2:uid="{5143E0EF-E74E-2148-B70D-CC51C941048D}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{5143E0EF-E74E-2148-B70D-CC51C941048D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="71">
   <si>
     <t>ID</t>
   </si>
@@ -47,48 +47,66 @@
     <t>Eye (OD/OS)</t>
   </si>
   <si>
+    <t>RL001</t>
+  </si>
+  <si>
+    <t>Mild</t>
+  </si>
+  <si>
+    <t>OS</t>
+  </si>
+  <si>
+    <t>RL002</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>OU</t>
+  </si>
+  <si>
+    <t>RL003</t>
+  </si>
+  <si>
+    <t>OD</t>
+  </si>
+  <si>
+    <t>RL004</t>
+  </si>
+  <si>
+    <t>RL006</t>
+  </si>
+  <si>
+    <t>RL007</t>
+  </si>
+  <si>
+    <t>RL008</t>
+  </si>
+  <si>
+    <t>RL010</t>
+  </si>
+  <si>
+    <t>RL011</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>RL012</t>
+  </si>
+  <si>
+    <t>RL013</t>
+  </si>
+  <si>
+    <t>RL014</t>
+  </si>
+  <si>
+    <t>RL015</t>
+  </si>
+  <si>
     <t>RL016</t>
   </si>
   <si>
-    <t>RL001</t>
-  </si>
-  <si>
-    <t>RL002</t>
-  </si>
-  <si>
-    <t>RL003</t>
-  </si>
-  <si>
-    <t>RL004</t>
-  </si>
-  <si>
-    <t>RL006</t>
-  </si>
-  <si>
-    <t>RL007</t>
-  </si>
-  <si>
-    <t>RL008</t>
-  </si>
-  <si>
-    <t>RL010</t>
-  </si>
-  <si>
-    <t>RL011</t>
-  </si>
-  <si>
-    <t>RL012</t>
-  </si>
-  <si>
-    <t>RL013</t>
-  </si>
-  <si>
-    <t>RL014</t>
-  </si>
-  <si>
-    <t>RL015</t>
-  </si>
-  <si>
     <t>RL017</t>
   </si>
   <si>
@@ -104,6 +122,9 @@
     <t>RL021</t>
   </si>
   <si>
+    <t>Moderate</t>
+  </si>
+  <si>
     <t>RL022</t>
   </si>
   <si>
@@ -128,27 +149,6 @@
     <t>RL029</t>
   </si>
   <si>
-    <t>Mild</t>
-  </si>
-  <si>
-    <t>OS</t>
-  </si>
-  <si>
-    <t>Control</t>
-  </si>
-  <si>
-    <t>OU</t>
-  </si>
-  <si>
-    <t>OD</t>
-  </si>
-  <si>
-    <t>Advanced</t>
-  </si>
-  <si>
-    <t>Moderate</t>
-  </si>
-  <si>
     <t>RL030</t>
   </si>
   <si>
@@ -189,13 +189,73 @@
   </si>
   <si>
     <t>RL043</t>
+  </si>
+  <si>
+    <t>RL044</t>
+  </si>
+  <si>
+    <t>RL045</t>
+  </si>
+  <si>
+    <t>RL046</t>
+  </si>
+  <si>
+    <t>RL047</t>
+  </si>
+  <si>
+    <t>RL048</t>
+  </si>
+  <si>
+    <t>RL049</t>
+  </si>
+  <si>
+    <t>RL050</t>
+  </si>
+  <si>
+    <t>RL051</t>
+  </si>
+  <si>
+    <t>RL052</t>
+  </si>
+  <si>
+    <t>RL053</t>
+  </si>
+  <si>
+    <t>RL055</t>
+  </si>
+  <si>
+    <t>RL056</t>
+  </si>
+  <si>
+    <t>RL057</t>
+  </si>
+  <si>
+    <t>RL058</t>
+  </si>
+  <si>
+    <t>RL059</t>
+  </si>
+  <si>
+    <t>RL060</t>
+  </si>
+  <si>
+    <t>RL061</t>
+  </si>
+  <si>
+    <t>RL062</t>
+  </si>
+  <si>
+    <t>RL064</t>
+  </si>
+  <si>
+    <t>RL065</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -582,13 +642,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F05934-8B03-F145-A217-B77ED63881D2}">
-  <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C62"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="21.95">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -599,455 +659,675 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>35</v>
       </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="C20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>29</v>
-      </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
